--- a/src/output/output_report.xlsx
+++ b/src/output/output_report.xlsx
@@ -471,7 +471,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3792,6 +3792,18 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>xlsx</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>output_report.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
